--- a/产品部门/各组sop/关务组-分单号规则表.xlsx
+++ b/产品部门/各组sop/关务组-分单号规则表.xlsx
@@ -8,12 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分单号规则主表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则模板抽象" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬约束与难点" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="硬约束与校验" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'分单号规则主表'!$A$1:$G$17</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +30,11 @@
       <b val="1"/>
       <color rgb="00595959"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -43,22 +43,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F6FFED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF7E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9F0FF"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,24 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,16 +447,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -511,12 +487,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>系统建议模板</t>
+          <t>系统建议</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>模板</t>
         </is>
       </c>
     </row>
@@ -538,20 +514,24 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>删掉提单号最后一位，再依次 +0、+1、+2、+3…</t>
+          <t>删掉提单号最后一位，再+0、1、2、3…；总位数不能变</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号[0..-2] + 序号(0,1,2,3…)</t>
+          <t>base=BL去末1位；分单号=base+0/1/2/3；len不变</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>T1 删末位+数字序号(从0)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>删末位+数字序号(从0)；校验位数</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -566,25 +546,29 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>可自动</t>
+          <t>可自动/超限确认</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>直接后面+A、B、C、D…（字母序）；超出26位（A–Z）要单独确认</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>票1-26=BL+A…Z；票≥27人工确认</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>后缀字母A–Z；超26位强制确认</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>T2x</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -594,7 +578,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>通用(未区分港口)</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -604,53 +588,61 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>第1票主单不变；从第2票起依次 +A、+B、+C、+D…</t>
+          <t>主单不变；第2票起依次+A、B、C、D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>票1=提单号；票N(N≥2)=提单号+字母</t>
+          <t>票1=BL；票N=BL+字母</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>T3 第1票=主单其后加字母</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>主单保留+从第2票加字母</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>以星</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>需申请/手填</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>需单独申请（一般放舱时申请）；不够可用其他提单的分单号</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>无固定公式 → 手填/申请池/借用他票</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>T7 人工申请/手填</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>需申请</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>单独申请；一般放舱时申请；不够可用其他提单分单号</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>无固定公式→手填/申请池/借用</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>放舱提醒；申请池与借用留痕</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -670,20 +662,24 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>直接后面+A、B、C、D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>BL+A/B/C/D…</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>后缀字母序号</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -703,20 +699,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>第1票主单不变；从第2票起 +01、+02、+03…</t>
+          <t>主单不变；第2票起+01、02、03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>票1=提单号；票N=提单号+01/02/03…</t>
+          <t>票1=BL；票N=BL+01/02/03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>T4 第1票=主单其后加两位数字</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>主单保留+两位数字</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>宁波</t>
+          <t>宁波/厦门</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -736,30 +736,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>直接后面+A、B、C、D；最后一票用Z</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>中间=BL+字母；末票=BL+Z</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>后缀字母；末票强制Z</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>T2z</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>COSCO/OOCL</t>
+          <t>COSCO</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -769,100 +773,108 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>最后一位0去掉，再+1、2、3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>base=去末位0；+1/2/3…</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>删末位0+数字(从1)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>T1b</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>COSCO/OOCL</t>
+          <t>WHL</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>青岛</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>需申请</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>单独申请</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>无固定公式→手填</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>放舱申请提醒</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>WHL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>宁波/厦门</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>可自动</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>去掉提单号最后一位0，再 +1、+2、+3…</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>去末位0(提单号)+数字(1,2,3…)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>T1 变体：删末位0+数字(从1)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>末位非0时兜底待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>WHL</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>需申请/手填</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>需单独申请</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>无固定公式 → 手填/申请后录入</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>T7 人工申请/手填</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>直接后面+A、B、C、D</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>BL+A/B/C/D…</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>后缀字母序号</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>WHL</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>宁波</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -872,30 +884,34 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>主单不变；第2票起去掉GLV，+A01、A02、A03</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>票1=BL；票N=去GLV+A01…</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>去GLV+A两位序号</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>WHL</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>宁波</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -905,20 +921,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>直接后面+A、B、C、D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>BL+A/B/C/D…</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>后缀字母序号</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -928,7 +948,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -938,126 +958,63 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>第1票主单不变；从第2票起去掉GLV，再 +A01、+A02、+A03…</t>
+          <t>去掉前缀EGLV，+A、B、C、D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>票1=提单号；票N=去GLV+A01/A02…</t>
+          <t>去EGLV+字母</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>T5 去片段GLV+A两位序号</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>去前缀+后缀字母</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>宁波</t>
+          <t>华南口岸</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>可自动</t>
+          <t>特殊</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>提单号后直接追加 A、B、C、D…</t>
+          <t>不做资料；资料打包给报关行；分单号以客户单号为准</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>分单号 = 提单号 + 字母(A,B,C,D…)</t>
+          <t>分单号=客户单号</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>T2 整单后缀字母</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>EMC</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>青岛</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>可自动</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>去掉前缀EGLV，再 +A、+B、+C、+D…</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>去前缀EGLV + 字母(A,B,C,D…)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>T6 去前缀EGLV+后缀字母</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>华南(区域)</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>华南口岸</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>特殊策略</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>不做资料；报关资料打包给报关行；系统分单号直接以单号为准</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>分单号 = 系统单号（口径待确认）</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>T8 等于系统单号</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>跳过Excel做资料路径</t>
+          <t>跳过做资料路径；绑定=客户单号</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>T8</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1068,312 +1025,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>模板编号</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>模板名称</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>逻辑</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>适用</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>硬约束</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>删末位 + 数字序号</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>base=BL去末位；base+start起递增</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>美森上海(start=0)；COSCO/OOCL青岛(删0,start=1)</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>分票顺序</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>顺序写错没关系</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>整单后缀字母</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>BL + A/B/C/D…（每票都加）</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>美森宁波；以星宁波；COSCO/OOCL宁波厦门；WHL宁波厦门；EMC宁波</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>分单号 vs 舱单</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>必须对上，否则改运抵</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>第1票=主单，其后加字母</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>票1=BL；票N=BL+字母</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>合德</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>第1票=主单，其后加两位数字</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>票1=BL；票N=BL+01/02/03…</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>COSCO/OOCL上海</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>华南</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>不做资料；分单号以客户单号为准</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>去片段 + 特殊后缀</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>第1票=BL；其后去GLV + A01/A02…</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>EMC上海</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>校验项</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>去前缀 + 后缀字母</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>去EGLV + A/B/C…</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>EMC青岛</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>船司+港口命中</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>未配置则强制手填</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>人工申请/手填</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>无公式；申请池或借用他票</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>以星上海；WHL上海</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T7不自动</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>以星上海/WHL上海</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>等于系统单号</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>不做资料；分单号=单号</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>华南</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>硬约束</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>分票顺序写错可接受，但分单号必须与舱单数据一致，否则会改运抵</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>现状操作</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>做资料时先自己填分单号 → 做资料 → 再去系统逐票绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>目标操作</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>系统按船司×港口自动生成 → 按系统分单号做资料 → 去掉逐票绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>难点1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>格式多变；能否自动准确；特殊分单号需单独申请并支持手填</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>难点2</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>合并报关分柜装时须提示并指定谁报，避免漏报/重复报</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>对应方案</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>GW-01 分单号按船司港口自动生成</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>舱单一致硬校验</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>不一致禁止静默提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>美森上海位数</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>len(分单号)==len(提单号)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>美森宁波超26位</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A–Z用尽后（第27票起）人工确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>COSCO/OOCL末票Z</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>宁波/厦门最后一票后缀Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>人工覆盖留痕</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>可改自动结果</t>
         </is>
       </c>
     </row>
